--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.52302072293467</v>
+        <v>7.234990867476885</v>
       </c>
       <c r="D2" t="n">
-        <v>44.79426926427709</v>
+        <v>7.279068755445027</v>
       </c>
       <c r="E2" t="n">
-        <v>16.46095256486365</v>
+        <v>2.674904791790343</v>
       </c>
       <c r="F2" t="n">
-        <v>16.45653172631997</v>
+        <v>2.674186405526996</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>82.83468796394676</v>
+        <v>13.46063679414135</v>
       </c>
       <c r="D3" t="n">
-        <v>83.12790549232487</v>
+        <v>13.50828464250279</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46095256486365</v>
+        <v>2.674904791790343</v>
       </c>
       <c r="F3" t="n">
-        <v>16.45653172631997</v>
+        <v>2.674186405526996</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.09952052339426</v>
+        <v>7.328672085051568</v>
       </c>
       <c r="D4" t="n">
-        <v>45.4360508315814</v>
+        <v>7.383358260131978</v>
       </c>
       <c r="E4" t="n">
-        <v>16.46095256486365</v>
+        <v>2.674904791790343</v>
       </c>
       <c r="F4" t="n">
-        <v>16.45653172631997</v>
+        <v>2.674186405526996</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.1260041704154</v>
+        <v>11.3954756776925</v>
       </c>
       <c r="D5" t="n">
-        <v>70.42206928176675</v>
+        <v>11.4435862582871</v>
       </c>
       <c r="E5" t="n">
-        <v>16.46095256486365</v>
+        <v>2.674904791790343</v>
       </c>
       <c r="F5" t="n">
-        <v>16.45653172631997</v>
+        <v>2.674186405526996</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
